--- a/data/trans_camb/IP2005-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 5,84</t>
+          <t>-14,07; 5,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 15,93</t>
+          <t>2,99; 15,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 13,14</t>
+          <t>-1,17; 12,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 11,18</t>
+          <t>-8,68; 11,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 16,7</t>
+          <t>-1,52; 16,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,08</t>
+          <t>0,67; 16,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,37</t>
+          <t>-8,07; 5,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,3</t>
+          <t>2,58; 13,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 12,24</t>
+          <t>2,1; 12,98</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 6,68</t>
+          <t>-14,97; 6,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 18,94</t>
+          <t>3,08; 18,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 15,6</t>
+          <t>-1,2; 14,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 13,32</t>
+          <t>-9,18; 13,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 20,47</t>
+          <t>-1,61; 19,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 21,32</t>
+          <t>0,97; 21,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 6,25</t>
+          <t>-8,64; 6,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 15,76</t>
+          <t>2,76; 15,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,52</t>
+          <t>2,31; 15,38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 12,98</t>
+          <t>-1,81; 13,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 20,77</t>
+          <t>7,0; 20,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 12,66</t>
+          <t>-4,79; 14,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 12,98</t>
+          <t>-2,72; 12,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 14,29</t>
+          <t>-1,53; 14,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 6,35</t>
+          <t>-13,97; 5,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 11,12</t>
+          <t>0,11; 11,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,16</t>
+          <t>5,0; 15,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 7,22</t>
+          <t>-5,99; 7,89</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 16,29</t>
+          <t>-1,91; 16,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 27,09</t>
+          <t>8,14; 25,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 16,38</t>
+          <t>-5,59; 18,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 16,68</t>
+          <t>-3,13; 16,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 18,37</t>
+          <t>-1,75; 18,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 8,03</t>
+          <t>-16,41; 7,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 13,97</t>
+          <t>0,21; 13,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 19,26</t>
+          <t>5,87; 19,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 8,94</t>
+          <t>-7,08; 9,98</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 1,79</t>
+          <t>-12,24; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,96</t>
+          <t>-7,1; 4,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,11; -2,13</t>
+          <t>-18,89; -2,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 5,52</t>
+          <t>-5,11; 5,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 5,61</t>
+          <t>-5,67; 5,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -3,38</t>
+          <t>-19,99; -3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 2,22</t>
+          <t>-5,98; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,24</t>
+          <t>-4,3; 3,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -5,23</t>
+          <t>-16,31; -4,95</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 1,91</t>
+          <t>-12,35; 1,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 4,2</t>
+          <t>-7,29; 5,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -2,13</t>
+          <t>-19,35; -2,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,88</t>
+          <t>-5,07; 5,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 5,99</t>
+          <t>-5,68; 5,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -3,54</t>
+          <t>-20,65; -3,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,35</t>
+          <t>-6,2; 2,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 3,4</t>
+          <t>-4,42; 3,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,26; -5,4</t>
+          <t>-16,83; -5,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -2,51</t>
+          <t>-17,23; -2,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 1,16</t>
+          <t>-12,57; 1,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -14,0</t>
+          <t>-34,12; -14,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,76; -0,11</t>
+          <t>-14,05; 0,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -3,27</t>
+          <t>-17,57; -2,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -5,2</t>
+          <t>-25,67; -4,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,15; -2,94</t>
+          <t>-13,68; -3,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,18; -2,59</t>
+          <t>-12,5; -2,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-26,81; -11,36</t>
+          <t>-27,02; -11,66</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,51; -2,74</t>
+          <t>-17,85; -3,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 1,2</t>
+          <t>-13,08; 0,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,34; -15,06</t>
+          <t>-35,31; -15,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -0,15</t>
+          <t>-14,51; -0,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -3,44</t>
+          <t>-18,15; -2,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,43; -5,48</t>
+          <t>-26,37; -5,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -3,17</t>
+          <t>-13,99; -3,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -2,74</t>
+          <t>-12,9; -2,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -11,77</t>
+          <t>-27,93; -12,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 17,74</t>
+          <t>-9,55; 18,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 20,45</t>
+          <t>-7,56; 18,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 23,29</t>
+          <t>0,49; 23,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 20,63</t>
+          <t>-6,49; 18,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 11,23</t>
+          <t>-17,56; 10,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 23,05</t>
+          <t>-0,92; 21,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 14,61</t>
+          <t>-3,9; 14,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 11,08</t>
+          <t>-8,46; 10,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 19,27</t>
+          <t>2,46; 19,05</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 24,48</t>
+          <t>-10,62; 25,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 28,42</t>
+          <t>-8,08; 26,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 32,62</t>
+          <t>0,51; 32,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 27,95</t>
+          <t>-7,22; 25,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 14,99</t>
+          <t>-19,64; 13,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 31,65</t>
+          <t>-0,86; 29,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 19,37</t>
+          <t>-4,36; 19,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 14,71</t>
+          <t>-9,71; 14,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,43; 25,71</t>
+          <t>2,88; 25,41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 7,93</t>
+          <t>-8,04; 7,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 7,24</t>
+          <t>-9,01; 7,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 5,2</t>
+          <t>-12,91; 4,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-24,32; -6,13</t>
+          <t>-24,7; -6,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,15</t>
+          <t>-7,37; 3,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -1,61</t>
+          <t>-15,03; -1,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 5,1</t>
+          <t>-3,43; 5,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 2,71</t>
+          <t>-7,89; 2,55</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 8,91</t>
+          <t>-8,27; 8,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 7,99</t>
+          <t>-9,32; 7,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 5,55</t>
+          <t>-13,32; 4,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,74; -6,39</t>
+          <t>-25,31; -6,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,07</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,3</t>
+          <t>-7,56; 3,3</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -1,7</t>
+          <t>-15,31; -1,83</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,43</t>
+          <t>-3,5; 6,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 2,9</t>
+          <t>-8,14; 2,72</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,87</t>
+          <t>-3,83; 8,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,04; 12,56</t>
+          <t>0,52; 11,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 3,14</t>
+          <t>-11,55; 2,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 10,55</t>
+          <t>-0,87; 9,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 9,69</t>
+          <t>-1,75; 9,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -0,43</t>
+          <t>-16,12; -1,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,83</t>
+          <t>-0,18; 8,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,7</t>
+          <t>0,83; 8,93</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,77; -1,2</t>
+          <t>-11,4; -1,07</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 10,24</t>
+          <t>-4,2; 10,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1,18; 14,97</t>
+          <t>0,61; 13,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 3,67</t>
+          <t>-12,67; 2,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 12,33</t>
+          <t>-0,89; 11,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 11,32</t>
+          <t>-1,83; 10,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -0,56</t>
+          <t>-17,48; -1,68</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 9,04</t>
+          <t>-0,18; 9,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,84; 10,04</t>
+          <t>0,91; 10,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -1,37</t>
+          <t>-12,52; -1,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,39</t>
+          <t>1,3; 13,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 9,46</t>
+          <t>-2,34; 10,07</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,12; 13,62</t>
+          <t>1,5; 13,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,44; 13,63</t>
+          <t>2,12; 13,71</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 11,13</t>
+          <t>-1,18; 10,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,68; 18,23</t>
+          <t>7,76; 18,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,45; 11,8</t>
+          <t>3,59; 12,07</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,11; 8,9</t>
+          <t>-0,1; 8,73</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,17; 14,63</t>
+          <t>6,92; 14,62</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,34; 15,36</t>
+          <t>1,65; 16,58</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 11,58</t>
+          <t>-2,68; 12,6</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,49; 16,99</t>
+          <t>1,86; 17,11</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2,86; 17,19</t>
+          <t>2,37; 17,08</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 14,03</t>
+          <t>-1,31; 13,58</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,7; 23,16</t>
+          <t>9,01; 23,09</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,97; 14,53</t>
+          <t>4,21; 14,86</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0,13; 11,13</t>
+          <t>-0,03; 10,86</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7,27; 18,12</t>
+          <t>8,02; 18,12</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,21</t>
+          <t>-1,24; 4,18</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,89</t>
+          <t>1,89; 7,08</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,73</t>
+          <t>-4,18; 2,23</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,65</t>
+          <t>-0,52; 4,81</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,01</t>
+          <t>-0,46; 4,84</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,14</t>
+          <t>-3,89; 2,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,53</t>
+          <t>-0,16; 3,62</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,18</t>
+          <t>1,47; 5,31</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,14</t>
+          <t>-3,15; 1,25</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,85</t>
+          <t>-1,37; 4,76</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,9</t>
+          <t>2,07; 8,16</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 1,97</t>
+          <t>-4,64; 2,56</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,34</t>
+          <t>-0,62; 5,52</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,77</t>
+          <t>-0,52; 5,51</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,44</t>
+          <t>-4,33; 2,44</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,99</t>
+          <t>-0,18; 4,12</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,94</t>
+          <t>1,64; 6,03</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,29</t>
+          <t>-3,55; 1,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 5,87</t>
+          <t>-14,32; 5,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 15,74</t>
+          <t>2,96; 16,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 12,74</t>
+          <t>-0,36; 13,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 11,27</t>
+          <t>-8,1; 10,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 16,08</t>
+          <t>-1,46; 16,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 16,75</t>
+          <t>1,74; 17,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 5,84</t>
+          <t>-8,02; 5,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,51</t>
+          <t>2,48; 12,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,98</t>
+          <t>2,24; 12,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 6,58</t>
+          <t>-15,24; 6,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 18,68</t>
+          <t>3,05; 20,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 14,93</t>
+          <t>-0,38; 16,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 13,57</t>
+          <t>-8,56; 12,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 19,62</t>
+          <t>-1,45; 19,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 21,61</t>
+          <t>1,88; 22,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 6,76</t>
+          <t>-8,6; 5,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 15,99</t>
+          <t>2,65; 15,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 15,38</t>
+          <t>2,41; 14,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 13,36</t>
+          <t>-2,19; 13,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 20,08</t>
+          <t>7,03; 20,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 14,36</t>
+          <t>-5,37; 13,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 12,95</t>
+          <t>-3,16; 12,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 14,38</t>
+          <t>-1,44; 14,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 5,64</t>
+          <t>-12,33; 7,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 11,0</t>
+          <t>0,05; 11,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 15,14</t>
+          <t>4,9; 15,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 7,89</t>
+          <t>-6,63; 7,39</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 16,88</t>
+          <t>-2,43; 17,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 25,63</t>
+          <t>8,12; 25,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 18,26</t>
+          <t>-6,15; 17,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 16,65</t>
+          <t>-3,52; 16,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 18,68</t>
+          <t>-1,62; 18,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 7,13</t>
+          <t>-14,36; 9,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 13,82</t>
+          <t>0,14; 14,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 19,09</t>
+          <t>5,7; 18,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 9,98</t>
+          <t>-7,61; 9,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 1,83</t>
+          <t>-10,76; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,73</t>
+          <t>-7,0; 4,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -2,09</t>
+          <t>-17,77; -1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 5,49</t>
+          <t>-4,24; 5,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 5,16</t>
+          <t>-5,48; 5,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,99; -3,17</t>
+          <t>-20,57; -3,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 2,29</t>
+          <t>-6,04; 2,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,47</t>
+          <t>-4,17; 3,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -4,95</t>
+          <t>-16,31; -5,04</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 1,89</t>
+          <t>-11,11; 1,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 5,1</t>
+          <t>-7,13; 4,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,35; -2,3</t>
+          <t>-18,05; -1,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 5,98</t>
+          <t>-4,27; 6,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 5,57</t>
+          <t>-5,59; 5,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,65; -3,34</t>
+          <t>-21,27; -3,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 2,42</t>
+          <t>-6,21; 2,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 3,68</t>
+          <t>-4,25; 3,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,83; -5,27</t>
+          <t>-16,69; -5,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,23; -2,75</t>
+          <t>-17,79; -2,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 1,02</t>
+          <t>-12,29; 0,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,12; -14,51</t>
+          <t>-34,34; -13,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 0,02</t>
+          <t>-15,13; -0,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,57; -2,7</t>
+          <t>-17,89; -2,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,67; -4,93</t>
+          <t>-26,64; -4,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -3,36</t>
+          <t>-13,1; -2,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -2,48</t>
+          <t>-13,2; -2,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-27,02; -11,66</t>
+          <t>-26,19; -10,75</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -3,05</t>
+          <t>-18,26; -2,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 0,98</t>
+          <t>-12,69; 0,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,31; -15,44</t>
+          <t>-35,68; -14,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -0,2</t>
+          <t>-15,58; -0,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -2,91</t>
+          <t>-18,66; -2,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,37; -5,24</t>
+          <t>-27,49; -5,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -3,65</t>
+          <t>-13,56; -3,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,9; -2,66</t>
+          <t>-13,65; -3,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,93; -12,14</t>
+          <t>-26,96; -10,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 18,51</t>
+          <t>-8,64; 18,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 18,6</t>
+          <t>-8,1; 18,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 23,8</t>
+          <t>-0,4; 24,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 18,86</t>
+          <t>-6,54; 19,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 10,53</t>
+          <t>-15,39; 10,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 21,51</t>
+          <t>-2,03; 21,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 14,92</t>
+          <t>-3,31; 15,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 10,9</t>
+          <t>-7,86; 10,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 19,05</t>
+          <t>2,54; 18,81</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 25,62</t>
+          <t>-9,84; 26,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 26,13</t>
+          <t>-8,78; 26,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,51; 32,77</t>
+          <t>-0,42; 33,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 25,55</t>
+          <t>-7,39; 26,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 13,63</t>
+          <t>-17,46; 14,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 29,44</t>
+          <t>-2,1; 30,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 19,42</t>
+          <t>-3,98; 19,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 14,14</t>
+          <t>-9,23; 13,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,88; 25,41</t>
+          <t>2,93; 24,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 7,21</t>
+          <t>-8,1; 8,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 7,19</t>
+          <t>-9,22; 7,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 4,26</t>
+          <t>-13,04; 4,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -6,09</t>
+          <t>-23,94; -6,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 6,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 3,15</t>
+          <t>-7,42; 2,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -1,72</t>
+          <t>-15,16; -2,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,7</t>
+          <t>-3,26; 5,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 2,55</t>
+          <t>-7,22; 2,76</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 8,0</t>
+          <t>-8,54; 9,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 7,89</t>
+          <t>-9,62; 7,84</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 4,76</t>
+          <t>-13,58; 4,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -6,36</t>
+          <t>-24,33; -6,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 3,3</t>
+          <t>-7,57; 2,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -1,83</t>
+          <t>-15,63; -2,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 6,14</t>
+          <t>-3,36; 5,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 2,72</t>
+          <t>-7,43; 2,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 8,94</t>
+          <t>-3,26; 9,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 11,41</t>
+          <t>0,68; 11,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 2,44</t>
+          <t>-11,85; 2,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 9,99</t>
+          <t>-0,89; 10,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,41</t>
+          <t>-1,58; 9,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,12; -1,48</t>
+          <t>-15,38; -0,38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 8,42</t>
+          <t>-0,37; 8,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,93</t>
+          <t>1,12; 9,11</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -1,07</t>
+          <t>-11,29; -0,92</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 10,43</t>
+          <t>-3,46; 11,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,61; 13,47</t>
+          <t>0,91; 14,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 2,78</t>
+          <t>-12,78; 2,83</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 11,68</t>
+          <t>-0,92; 11,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 10,94</t>
+          <t>-1,7; 11,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -1,68</t>
+          <t>-16,7; -0,44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,73</t>
+          <t>-0,38; 9,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,35</t>
+          <t>1,22; 10,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,52; -1,29</t>
+          <t>-12,5; -1,07</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,3; 13,08</t>
+          <t>0,86; 13,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 10,07</t>
+          <t>-2,97; 9,27</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,62</t>
+          <t>1,72; 14,51</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,12; 13,71</t>
+          <t>2,5; 13,38</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 10,8</t>
+          <t>-1,14; 11,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,76; 18,2</t>
+          <t>8,09; 17,97</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,59; 12,07</t>
+          <t>3,45; 12,05</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 8,73</t>
+          <t>-0,17; 8,88</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,62</t>
+          <t>6,56; 14,43</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,65; 16,58</t>
+          <t>1,04; 16,41</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 12,6</t>
+          <t>-3,34; 11,59</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1,86; 17,11</t>
+          <t>2,02; 18,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2,37; 17,08</t>
+          <t>2,91; 16,76</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 13,58</t>
+          <t>-1,27; 14,16</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,01; 23,09</t>
+          <t>9,3; 22,56</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,86</t>
+          <t>4,03; 14,88</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 10,86</t>
+          <t>-0,18; 11,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>8,02; 18,12</t>
+          <t>7,63; 17,95</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,18</t>
+          <t>-1,18; 4,09</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,08</t>
+          <t>1,95; 7,03</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,23</t>
+          <t>-3,98; 2,17</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,81</t>
+          <t>-0,38; 4,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,84</t>
+          <t>-0,5; 5,09</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,14</t>
+          <t>-3,93; 2,19</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,62</t>
+          <t>-0,06; 3,77</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,31</t>
+          <t>1,53; 5,27</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,25</t>
+          <t>-2,92; 1,37</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,76</t>
+          <t>-1,31; 4,66</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,16</t>
+          <t>2,17; 8,08</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,56</t>
+          <t>-4,41; 2,46</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,52</t>
+          <t>-0,42; 5,46</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,51</t>
+          <t>-0,56; 5,87</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,44</t>
+          <t>-4,34; 2,52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,12</t>
+          <t>-0,07; 4,31</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,03</t>
+          <t>1,71; 6,01</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,42</t>
+          <t>-3,25; 1,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,73</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,71</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-3,72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,73</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>6,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 5,88</t>
+          <t>-8,04; 11,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,68</t>
+          <t>-0,99; 16,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 13,76</t>
+          <t>1,48; 16,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 10,38</t>
+          <t>-13,38; 5,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 16,11</t>
+          <t>3,43; 15,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 17,93</t>
+          <t>-0,91; 12,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 5,25</t>
+          <t>-8,17; 5,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 12,93</t>
+          <t>2,46; 13,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 12,3</t>
+          <t>1,77; 11,87</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-4,04%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>8,81%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 6,79</t>
+          <t>-8,65; 13,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 20,02</t>
+          <t>-0,99; 20,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 16,45</t>
+          <t>1,56; 20,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 12,52</t>
+          <t>-14,04; 6,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 19,87</t>
+          <t>3,56; 18,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 22,26</t>
+          <t>-0,98; 15,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,97</t>
+          <t>-8,76; 6,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,05</t>
+          <t>2,64; 15,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 14,31</t>
+          <t>1,94; 13,98</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,53</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,02</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,48</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,69</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>-1,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 13,59</t>
+          <t>-2,81; 12,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 20,16</t>
+          <t>-0,48; 14,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 13,68</t>
+          <t>-12,67; 5,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 12,57</t>
+          <t>-2,52; 12,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 14,38</t>
+          <t>8,02; 20,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 7,19</t>
+          <t>-8,98; 8,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 11,12</t>
+          <t>-0,14; 11,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 15,03</t>
+          <t>5,03; 15,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 7,39</t>
+          <t>-8,31; 4,55</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-4,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,2%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>16,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-3,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>-2,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 17,35</t>
+          <t>-3,11; 16,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 25,96</t>
+          <t>-0,49; 18,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 17,52</t>
+          <t>-14,89; 7,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 16,04</t>
+          <t>-2,87; 16,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 18,47</t>
+          <t>9,11; 27,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 9,16</t>
+          <t>-10,16; 10,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 14,01</t>
+          <t>-0,13; 13,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,94</t>
+          <t>5,91; 19,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 9,29</t>
+          <t>-9,7; 6,0</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-9,61</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,76</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-9,32</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,96</t>
+          <t>-8,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,21</t>
+          <t>-9,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 1,88</t>
+          <t>-5,07; 5,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,15</t>
+          <t>-5,14; 5,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -1,67</t>
+          <t>-17,66; -2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,75</t>
+          <t>-11,12; 1,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 5,47</t>
+          <t>-6,9; 3,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -3,26</t>
+          <t>-17,48; -1,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,02</t>
+          <t>-6,3; 2,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,4</t>
+          <t>-4,14; 3,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -5,04</t>
+          <t>-15,17; -4,36</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-9,98%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-4,19%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-0,79%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-9,63%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-11,38%</t>
+          <t>-9,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-10,58%</t>
+          <t>-9,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 1,96</t>
+          <t>-5,12; 5,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 4,39</t>
+          <t>-5,24; 5,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,05; -1,77</t>
+          <t>-18,29; -3,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 6,12</t>
+          <t>-11,37; 1,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 5,87</t>
+          <t>-7,07; 4,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,27; -3,51</t>
+          <t>-18,04; -1,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 2,12</t>
+          <t>-6,4; 2,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 3,63</t>
+          <t>-4,23; 3,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,69; -5,27</t>
+          <t>-15,71; -4,65</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-6,62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-9,68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-15,2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-9,3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-5,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-23,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-6,62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-9,68</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-14,72</t>
+          <t>-22,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-18,77</t>
+          <t>-19,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -2,57</t>
+          <t>-13,76; -0,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 0,77</t>
+          <t>-18,38; -3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,34; -13,65</t>
+          <t>-26,91; -6,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -0,69</t>
+          <t>-18,0; -2,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,89; -2,34</t>
+          <t>-12,59; 1,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,64; -4,87</t>
+          <t>-32,31; -13,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -2,81</t>
+          <t>-13,15; -2,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -2,96</t>
+          <t>-13,18; -2,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -10,75</t>
+          <t>-27,23; -11,76</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-6,88%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-10,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-15,8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-9,74%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-5,41%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-24,23%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-6,88%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-10,06%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,3%</t>
+          <t>-23,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-19,57%</t>
+          <t>-19,84%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,26; -2,77</t>
+          <t>-14,14; -0,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 0,82</t>
+          <t>-18,87; -3,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,68; -14,39</t>
+          <t>-27,34; -6,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -0,84</t>
+          <t>-18,51; -2,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,66; -2,58</t>
+          <t>-12,9; 1,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,49; -5,22</t>
+          <t>-33,9; -14,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -3,02</t>
+          <t>-13,64; -3,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,65; -3,15</t>
+          <t>-13,49; -2,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,96; -10,74</t>
+          <t>-28,08; -12,36</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,38</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,71</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,85</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10,98</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6,38</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,34</t>
+          <t>10,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 18,81</t>
+          <t>-5,47; 20,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 18,87</t>
+          <t>-17,72; 11,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 24,03</t>
+          <t>-0,76; 22,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 19,39</t>
+          <t>-9,8; 17,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 10,67</t>
+          <t>-6,82; 20,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 21,31</t>
+          <t>-0,05; 23,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 15,01</t>
+          <t>-4,49; 14,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 10,51</t>
+          <t>-7,67; 11,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 18,81</t>
+          <t>2,9; 19,38</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-3,28%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-3,28%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 26,43</t>
+          <t>-6,2; 27,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 26,37</t>
+          <t>-20,02; 14,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 33,98</t>
+          <t>-0,12; 31,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 26,38</t>
+          <t>-10,89; 24,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 14,67</t>
+          <t>-7,6; 28,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 30,09</t>
+          <t>-0,01; 32,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 19,71</t>
+          <t>-4,79; 19,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 13,54</t>
+          <t>-8,71; 14,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,93; 24,61</t>
+          <t>3,3; 25,55</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-14,17</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2,17</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-1,64</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-0,21</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-0,23</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-14,17</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-4,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-2,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 8,14</t>
+          <t>-24,32; -6,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 7,1</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 4,01</t>
+          <t>-7,89; 3,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-23,94; -6,0</t>
+          <t>-8,41; 7,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,56</t>
+          <t>-9,51; 7,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 2,84</t>
+          <t>-13,15; 4,6</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -2,2</t>
+          <t>-13,45; -1,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,47</t>
+          <t>-3,22; 5,1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 2,76</t>
+          <t>-8,42; 2,49</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-14,48%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-1,68%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-0,22%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-0,25%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-3,86%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-14,48%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>-4,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-2,45%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 9,31</t>
+          <t>-24,74; -6,39</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 7,84</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 4,45</t>
+          <t>-7,99; 3,31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,33; -6,29</t>
+          <t>-8,69; 8,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>-9,65; 7,99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 2,97</t>
+          <t>-13,69; 4,99</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-15,63; -2,49</t>
+          <t>-13,93; -1,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,92</t>
+          <t>-3,27; 5,43</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 2,95</t>
+          <t>-8,61; 2,62</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3,78</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-8,85</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2,95</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>6,26</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,14</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4,7</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3,78</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,01</t>
+          <t>-4,67</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>-6,89</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,63</t>
+          <t>-0,61; 10,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 11,94</t>
+          <t>-1,91; 9,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 2,43</t>
+          <t>-17,22; -1,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 10,16</t>
+          <t>-3,74; 8,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 9,75</t>
+          <t>1,04; 12,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -0,38</t>
+          <t>-12,36; 2,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 8,31</t>
+          <t>-0,42; 7,83</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,11</t>
+          <t>0,74; 8,7</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,92</t>
+          <t>-12,29; -2,08</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-9,86%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>3,31%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>7,03%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-4,65%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-8,92%</t>
+          <t>-5,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-7,0%</t>
+          <t>-7,71%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 11,39</t>
+          <t>-0,65; 12,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,91; 14,35</t>
+          <t>-2,04; 11,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 2,83</t>
+          <t>-18,8; -1,65</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 11,89</t>
+          <t>-4,02; 10,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,37</t>
+          <t>1,18; 14,97</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -0,44</t>
+          <t>-13,54; 3,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,59</t>
+          <t>-0,37; 9,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,55</t>
+          <t>0,84; 10,04</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -1,07</t>
+          <t>-13,44; -2,37</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>7,87</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4,95</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>13,24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>6,81</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>3,63</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>4,95</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,88</t>
+          <t>8,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10,62</t>
+          <t>10,88</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,86; 13,0</t>
+          <t>2,44; 13,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 9,27</t>
+          <t>-1,27; 11,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,72; 14,51</t>
+          <t>8,11; 18,65</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,5; 13,38</t>
+          <t>1,18; 12,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 11,29</t>
+          <t>-3,07; 9,46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,09; 17,97</t>
+          <t>2,44; 14,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,05</t>
+          <t>3,45; 11,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,88</t>
+          <t>0,11; 8,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,43</t>
+          <t>6,54; 14,88</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>8,08%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,04; 16,41</t>
+          <t>2,86; 17,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 11,59</t>
+          <t>-1,47; 14,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,02; 18,28</t>
+          <t>9,33; 23,75</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2,91; 16,76</t>
+          <t>1,34; 15,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 14,16</t>
+          <t>-3,49; 11,58</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,3; 22,56</t>
+          <t>2,74; 17,38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,03; 14,88</t>
+          <t>3,97; 14,53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 11,07</t>
+          <t>0,13; 11,13</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,95</t>
+          <t>7,55; 18,39</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2,08</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>4,39</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,09</t>
+          <t>-0,7; 4,65</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,03</t>
+          <t>-0,4; 5,01</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,17</t>
+          <t>-3,88; 2,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,76</t>
+          <t>-1,26; 4,21</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,09</t>
+          <t>1,69; 6,89</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,19</t>
+          <t>-4,88; 1,07</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,77</t>
+          <t>-0,23; 3,53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,27</t>
+          <t>1,42; 5,18</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,37</t>
+          <t>-3,3; 0,73</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-1,0%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-1,15%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0,93%</t>
+          <t>-1,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,03%</t>
+          <t>-1,41%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,66</t>
+          <t>-0,77; 5,34</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,08</t>
+          <t>-0,45; 5,77</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,46</t>
+          <t>-4,31; 2,36</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,46</t>
+          <t>-1,4; 4,85</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,87</t>
+          <t>1,88; 7,9</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,52</t>
+          <t>-5,4; 1,24</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,31</t>
+          <t>-0,26; 3,99</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,01</t>
+          <t>1,58; 5,94</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,56</t>
+          <t>-3,66; 0,83</t>
         </is>
       </c>
     </row>
